--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,13 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -515,16 +524,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -629,16 +638,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>74.19</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,16 +664,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -675,16 +690,19 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>34</v>
       </c>
-      <c r="E4">
-        <v>34</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -698,16 +716,19 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>32</v>
       </c>
-      <c r="E5">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -763,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -789,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -815,13 +836,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -850,7 +871,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -892,24 +913,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920165</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -82,16 +82,25 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>ROBERTO</t>
@@ -881,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,10 +928,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -936,16 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920165</v>
+        <v>21330051920163</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -954,6 +963,29 @@
         <v>10</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920165</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -85,25 +85,16 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
     <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
   </si>
 </sst>
 </file>
@@ -890,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,10 +919,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,10 +942,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -963,29 +954,6 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920165</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,25 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
-    <t>MIGUEL</t>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
 </sst>
 </file>
@@ -784,16 +790,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>77.42</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -819,7 +825,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -871,7 +877,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,7 +928,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -936,7 +942,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920163</v>
+        <v>21330051920165</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -945,7 +951,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -954,6 +960,29 @@
         <v>10</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920386</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -79,25 +79,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>LORENZO</t>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
-    <t>ROBERTO</t>
+    <t>SALVADOR</t>
   </si>
   <si>
     <t>GREGORIO</t>
@@ -887,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,16 +934,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920156</v>
+        <v>21330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -948,10 +963,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -965,25 +980,71 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
+        <v>21330051920156</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920168</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>21330051920386</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G4">
-        <v>2</v>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
